--- a/EIB/Put_Location_v46.0.xlsx
+++ b/EIB/Put_Location_v46.0.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Location" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5098,12 +5098,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Perdoor</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BUSINESS SITE</t>
+          <t>BUSINESS ASSET</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>22.214358</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>114.154601</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="AR6" t="n">
@@ -5143,7 +5163,7 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5151,22 +5171,38 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7104</v>
+        <v>7103</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hiriyadka</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BUSINESS ASSET</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
       <c r="AR7" t="n">
         <v>1</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="BS7" t="n">
@@ -5198,7 +5234,7 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5206,22 +5242,36 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7105</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Karkala</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+        <v>7103</v>
+      </c>
+      <c r="H8" t="n">
         <v/>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXTENDED ENTERPRISE AFFILIATION	 </t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
       <c r="AR8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="BS8" t="n">
@@ -5253,7 +5303,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5261,22 +5311,44 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7106</v>
+        <v>7104</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Udupi</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v/>
+          <t>Hiriyadka</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BUSINESS ASSET</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>48.632896</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2.29228</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="BS9" t="n">
@@ -5308,7 +5380,7 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5316,16 +5388,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7103</v>
+        <v>7105</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Perdoor</t>
+          <t>Karkala</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BUSINESS SITE</t>
+          <t xml:space="preserve">EXTENDED ENTERPRISE AFFILIATION	 </t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>37.872512</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>-122.40881</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="AR10" t="n">
@@ -5333,7 +5425,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="BS10" t="n">
@@ -5365,7 +5457,7 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5373,16 +5465,36 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7103</v>
+        <v>7106</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Perdoor</t>
+          <t>Udupi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BUSINESS SITE</t>
+          <t xml:space="preserve">EXTENDED ENTERPRISE AFFILIATION	 </t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>23.251753</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>13.543276</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="AR11" t="n">
@@ -5390,7 +5502,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="BS11" t="n">

--- a/EIB/Put_Location_v46.0.xlsx
+++ b/EIB/Put_Location_v46.0.xlsx
@@ -5121,11 +5121,6 @@
           <t>INR</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="AR6" t="n">
         <v>1</v>
       </c>
@@ -5192,11 +5187,6 @@
       <c r="V7" t="n">
         <v/>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="AR7" t="n">
         <v>1</v>
       </c>
@@ -5244,8 +5234,10 @@
       <c r="F8" t="n">
         <v>7103</v>
       </c>
-      <c r="H8" t="n">
-        <v/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -5260,11 +5252,6 @@
       </c>
       <c r="V8" t="n">
         <v/>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
       </c>
       <c r="AR8" t="n">
         <v>1</v>
@@ -5338,11 +5325,6 @@
           <t>INR</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="AR9" t="n">
         <v>1</v>
       </c>
@@ -5415,11 +5397,6 @@
           <t>INR</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="AR10" t="n">
         <v>1</v>
       </c>
@@ -5490,11 +5467,6 @@
       <c r="V11" t="inlineStr">
         <is>
           <t>INR</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
       <c r="AR11" t="n">

--- a/EIB/Put_Location_v46.0.xlsx
+++ b/EIB/Put_Location_v46.0.xlsx
@@ -5178,15 +5178,6 @@
           <t>BUSINESS ASSET</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
       <c r="AR7" t="n">
         <v>1</v>
       </c>
@@ -5234,24 +5225,10 @@
       <c r="F8" t="n">
         <v>7103</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">EXTENDED ENTERPRISE AFFILIATION	 </t>
         </is>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
       </c>
       <c r="AR8" t="n">
         <v>1</v>

--- a/EIB/Put_Location_v46.0.xlsx
+++ b/EIB/Put_Location_v46.0.xlsx
@@ -5121,6 +5121,11 @@
           <t>INR</t>
         </is>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AR6" t="n">
         <v>1</v>
       </c>
@@ -5178,6 +5183,11 @@
           <t>BUSINESS ASSET</t>
         </is>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AR7" t="n">
         <v>1</v>
       </c>
@@ -5230,6 +5240,11 @@
           <t xml:space="preserve">EXTENDED ENTERPRISE AFFILIATION	 </t>
         </is>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AR8" t="n">
         <v>1</v>
       </c>
@@ -5302,6 +5317,11 @@
           <t>INR</t>
         </is>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AR9" t="n">
         <v>1</v>
       </c>
@@ -5374,6 +5394,11 @@
           <t>INR</t>
         </is>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AR10" t="n">
         <v>1</v>
       </c>
@@ -5444,6 +5469,11 @@
       <c r="V11" t="inlineStr">
         <is>
           <t>INR</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="AR11" t="n">

--- a/EIB/Put_Location_v46.0.xlsx
+++ b/EIB/Put_Location_v46.0.xlsx
@@ -5096,6 +5096,11 @@
       <c r="F6" t="n">
         <v>7103</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Mumbai</t>
@@ -5119,45 +5124,6 @@
       <c r="V6" t="inlineStr">
         <is>
           <t>INR</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="BS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>BUSINESS</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>COMMUNICATION_USAGE_BEHAVIOR_TENANTED-6-10</t>
         </is>
       </c>
     </row>
@@ -5173,6 +5139,11 @@
       <c r="F7" t="n">
         <v>7103</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Mumbai</t>
@@ -5181,45 +5152,6 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>BUSINESS ASSET</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="BS7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BU7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>BUSINESS</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>COMMUNICATION_USAGE_BEHAVIOR_TENANTED-6-10</t>
         </is>
       </c>
     </row>
@@ -5235,48 +5167,19 @@
       <c r="F8" t="n">
         <v>7103</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">EXTENDED ENTERPRISE AFFILIATION	 </t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AR8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="BS8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BU8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>BUSINESS</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>COMMUNICATION_USAGE_BEHAVIOR_TENANTED-6-10</t>
         </is>
       </c>
     </row>
@@ -5292,6 +5195,11 @@
       <c r="F9" t="n">
         <v>7104</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Hiriyadka</t>
@@ -5315,45 +5223,6 @@
       <c r="V9" t="inlineStr">
         <is>
           <t>INR</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="BS9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BU9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>BUSINESS</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>COMMUNICATION_USAGE_BEHAVIOR_TENANTED-6-10</t>
         </is>
       </c>
     </row>
@@ -5369,6 +5238,11 @@
       <c r="F10" t="n">
         <v>7105</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Karkala</t>
@@ -5392,45 +5266,6 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>INR</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="BS10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BU10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>BUSINESS</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>COMMUNICATION_USAGE_BEHAVIOR_TENANTED-6-10</t>
         </is>
       </c>
     </row>
@@ -5446,6 +5281,11 @@
       <c r="F11" t="n">
         <v>7106</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Udupi</t>
@@ -5469,45 +5309,6 @@
       <c r="V11" t="inlineStr">
         <is>
           <t>INR</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="BS11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BU11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>BUSINESS</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>COMMUNICATION_USAGE_BEHAVIOR_TENANTED-6-10</t>
         </is>
       </c>
     </row>
